--- a/ai4sh/import_data/utility/observation/excel/indicator.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="215">
   <si>
     <t xml:space="preserve">quantity_id__quantity_name</t>
   </si>
@@ -43,9 +43,6 @@
     <t xml:space="preserve">spectra array</t>
   </si>
   <si>
-    <t xml:space="preserve">spectra_array</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spectra array</t>
   </si>
   <si>
@@ -88,16 +85,13 @@
     <t xml:space="preserve">sm</t>
   </si>
   <si>
-    <t xml:space="preserve">soil cylinder drying@105c soil moisture volumetric content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cylinder soil moisture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penetrometer soil moisture volumetric content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penetrometer soil moisture</t>
+    <t xml:space="preserve">soil moisture volumetric content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil moisture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil moisture volumetric content</t>
   </si>
   <si>
     <t xml:space="preserve">temp</t>
@@ -503,9 +497,6 @@
   </si>
   <si>
     <t xml:space="preserve">soil moisture content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil moisture</t>
   </si>
   <si>
     <t xml:space="preserve">bulk density</t>
@@ -966,11 +957,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.33"/>
@@ -1002,147 +993,147 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
@@ -1150,16 +1141,16 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1167,195 +1158,195 @@
         <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>28</v>
+      <c r="A17" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="D25" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1366,15 +1357,15 @@
         <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>69</v>
@@ -1388,7 +1379,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>71</v>
@@ -1402,7 +1393,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>73</v>
@@ -1416,7 +1407,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>75</v>
@@ -1430,7 +1421,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>77</v>
@@ -1444,7 +1435,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>79</v>
@@ -1458,7 +1449,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>81</v>
@@ -1472,7 +1463,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>83</v>
@@ -1480,8 +1471,8 @@
       <c r="C36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>84</v>
+      <c r="D36" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1489,74 +1480,74 @@
         <v>85</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>85</v>
+      <c r="D37" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>96</v>
+      <c r="A41" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>100</v>
@@ -1570,10 +1561,10 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>103</v>
@@ -1590,29 +1581,29 @@
         <v>105</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>110</v>
@@ -1626,35 +1617,35 @@
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>118</v>
@@ -1668,7 +1659,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>120</v>
@@ -1682,7 +1673,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>122</v>
@@ -1696,16 +1687,16 @@
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1713,7 +1704,7 @@
         <v>104</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>126</v>
@@ -1724,7 +1715,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>127</v>
@@ -1738,7 +1729,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>129</v>
@@ -1752,21 +1743,21 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>133</v>
@@ -1780,7 +1771,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>135</v>
@@ -1794,7 +1785,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>137</v>
@@ -1807,151 +1798,151 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" s="1" t="s">
+      <c r="A60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="B60" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>140</v>
+      <c r="C60" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>156</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>27</v>
+        <v>155</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>163</v>
@@ -1962,24 +1953,24 @@
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C71" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>167</v>
@@ -1989,56 +1980,56 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>169</v>
+      <c r="A73" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>173</v>
@@ -2046,69 +2037,69 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="D78" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>179</v>
+      <c r="D79" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>183</v>
+      <c r="D80" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>185</v>
@@ -2129,142 +2120,125 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>190</v>
+      <c r="B83" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>189</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="D85" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="D86" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="D87" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>207</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>217</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" display="soil cylinder drying@105c soil moisture volumetric content"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/ai4sh/import_data/utility/observation/excel/indicator.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="234">
   <si>
     <t xml:space="preserve">quantity_id__quantity_name</t>
   </si>
@@ -665,6 +665,63 @@
   </si>
   <si>
     <t xml:space="preserve">Bacteria relative microbial content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification with nominative value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture class IUSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IUSS soil texture classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture class USDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USDA soil texture classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture usda major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture class iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil texture iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil texture iuss major group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compilation of 2 or more source datasets to a single dataset</t>
   </si>
 </sst>
 </file>
@@ -957,7 +1014,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.36"/>
@@ -2238,6 +2295,102 @@
         <v>214</v>
       </c>
     </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/ai4sh/import_data/utility/observation/excel/indicator.xlsx
+++ b/ai4sh/import_data/utility/observation/excel/indicator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="236">
   <si>
     <t xml:space="preserve">quantity_id__quantity_name</t>
   </si>
@@ -554,6 +554,12 @@
   </si>
   <si>
     <t xml:space="preserve">m shape parameter retention curve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil water tension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gravitational water rate</t>
   </si>
   <si>
     <t xml:space="preserve">proportion</t>
@@ -731,7 +737,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -766,6 +772,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -810,7 +821,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -828,6 +839,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1014,11 +1029,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.33"/>
@@ -2124,271 +2139,299 @@
       <c r="A79" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>182</v>
+      <c r="B80" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B85" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B95" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E95" s="1" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>233</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
